--- a/GF_X-master/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/GF_X-master/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>BRAKE</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>引擎</t>
+  </si>
+  <si>
+    <t>FailGame</t>
+  </si>
+  <si>
+    <t>你被老闆發現，立刻被開除了，從此流落街頭，點擊重來逆轉時間</t>
   </si>
   <si>
     <t>GET</t>
@@ -118,6 +124,12 @@
     <t>點擊開始</t>
   </si>
   <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>幹得漂亮！</t>
+  </si>
+  <si>
     <t>Nothing</t>
   </si>
   <si>
@@ -140,12 +152,6 @@
   </si>
   <si>
     <t>取消</t>
-  </si>
-  <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>喜歡這款遊戲嗎？ \n請給個5星好評吧！</t>
   </si>
   <si>
     <t>RatingDialog.HighRatingTips</t>
@@ -238,6 +244,12 @@
     <t>駕駛</t>
   </si>
   <si>
+    <t>SuccessGame</t>
+  </si>
+  <si>
+    <t>你成功俘獲了老闆女兒的芳心，立刻迎娶了白富美，從此走向人生巔峰</t>
+  </si>
+  <si>
     <t>TermsOfService</t>
   </si>
   <si>
@@ -247,13 +259,13 @@
     <t>Test123</t>
   </si>
   <si>
-    <t>測試語言掃描</t>
+    <t>程式碼測試語言掃描</t>
   </si>
   <si>
-    <t>Test1234</t>
+    <t>TipStart</t>
   </si>
   <si>
-    <t/>
+    <t>點擊小明小美親吻，但是小心老闆看見！ 另外注意門和窗戶啦！</t>
   </si>
   <si>
     <t>UNLOCK</t>
@@ -423,6 +435,14 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -2198,6 +2218,1002 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2214,265 +3230,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1058">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1059">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1060">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -2547,18 +3305,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1062">
+            <xdr:cNvPr hidden="1" name="A2" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -2633,18 +3391,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1063">
+            <xdr:cNvPr hidden="1" name="A3" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -2719,18 +3477,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1064">
+            <xdr:cNvPr hidden="1" name="A4" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -2805,18 +3563,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1065">
+            <xdr:cNvPr hidden="1" name="A5" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -2891,18 +3649,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1066">
+            <xdr:cNvPr hidden="1" name="A6" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -2977,18 +3735,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1067">
+            <xdr:cNvPr hidden="1" name="A7" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -3063,18 +3821,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1068">
+            <xdr:cNvPr hidden="1" name="A8" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -3149,18 +3907,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1069">
+            <xdr:cNvPr hidden="1" name="A9" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -3235,18 +3993,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1070">
+            <xdr:cNvPr hidden="1" name="A10" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -3321,18 +4079,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1071">
+            <xdr:cNvPr hidden="1" name="A11" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -3407,18 +4165,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1072">
+            <xdr:cNvPr hidden="1" name="A12" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -3493,18 +4251,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1073">
+            <xdr:cNvPr hidden="1" name="A13" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -3579,18 +4337,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1074">
+            <xdr:cNvPr hidden="1" name="A14" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -3665,18 +4423,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1075">
+            <xdr:cNvPr hidden="1" name="A15" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -3751,18 +4509,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1076">
+            <xdr:cNvPr hidden="1" name="A16" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -3837,18 +4595,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1077">
+            <xdr:cNvPr hidden="1" name="A17" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -3923,18 +4681,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1078">
+            <xdr:cNvPr hidden="1" name="A18" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4009,18 +4767,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1079">
+            <xdr:cNvPr hidden="1" name="A19" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4095,18 +4853,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1080">
+            <xdr:cNvPr hidden="1" name="A20" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4181,18 +4939,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1081">
+            <xdr:cNvPr hidden="1" name="A21" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -4267,18 +5025,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1082">
+            <xdr:cNvPr hidden="1" name="A22" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -4353,18 +5111,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1083">
+            <xdr:cNvPr hidden="1" name="A23" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -4439,18 +5197,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1084">
+            <xdr:cNvPr hidden="1" name="A24" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -4525,18 +5283,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1085">
+            <xdr:cNvPr hidden="1" name="A25" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -4611,18 +5369,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1086">
+            <xdr:cNvPr hidden="1" name="A26" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -4697,18 +5455,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1087">
+            <xdr:cNvPr hidden="1" name="A27" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -4783,18 +5541,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1088">
+            <xdr:cNvPr hidden="1" name="A28" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -4869,18 +5627,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1089">
+            <xdr:cNvPr hidden="1" name="A29" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -4955,6 +5713,264 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1090">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A31" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A32" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -4966,10 +5982,182 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1090">
+            <xdr:cNvPr hidden="1" name="A33" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5301,12 +6489,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
-    <col min="3" max="3" width="42.2229309082031" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5606,6 +6794,24 @@
         <v>65</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1"/>
+      <c r="B34" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1"/>
+      <c r="B35" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5618,7 +6824,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId428" name="A1">
+            <control shapeId="1061" r:id="rId670" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5640,7 +6846,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId429" name="A2">
+            <control shapeId="1062" r:id="rId671" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5662,7 +6868,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId430" name="A3">
+            <control shapeId="1063" r:id="rId672" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5684,7 +6890,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId431" name="A4">
+            <control shapeId="1064" r:id="rId673" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5706,7 +6912,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId432" name="A5">
+            <control shapeId="1065" r:id="rId674" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5728,7 +6934,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId433" name="A6">
+            <control shapeId="1066" r:id="rId675" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5750,7 +6956,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId434" name="A7">
+            <control shapeId="1067" r:id="rId676" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5772,7 +6978,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId435" name="A8">
+            <control shapeId="1068" r:id="rId677" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5794,7 +7000,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId436" name="A9">
+            <control shapeId="1069" r:id="rId678" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5816,7 +7022,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId437" name="A10">
+            <control shapeId="1070" r:id="rId679" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5838,7 +7044,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId438" name="A11">
+            <control shapeId="1071" r:id="rId680" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5860,7 +7066,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId439" name="A12">
+            <control shapeId="1072" r:id="rId681" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5882,7 +7088,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId440" name="A13">
+            <control shapeId="1073" r:id="rId682" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5904,7 +7110,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId441" name="A14">
+            <control shapeId="1074" r:id="rId683" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5926,7 +7132,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId442" name="A15">
+            <control shapeId="1075" r:id="rId684" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5948,7 +7154,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId443" name="A16">
+            <control shapeId="1076" r:id="rId685" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5970,7 +7176,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId444" name="A17">
+            <control shapeId="1077" r:id="rId686" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5992,7 +7198,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId445" name="A18">
+            <control shapeId="1078" r:id="rId687" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6014,7 +7220,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId446" name="A19">
+            <control shapeId="1079" r:id="rId688" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6036,7 +7242,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId447" name="A20">
+            <control shapeId="1080" r:id="rId689" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6058,7 +7264,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId448" name="A21">
+            <control shapeId="1081" r:id="rId690" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6080,7 +7286,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId449" name="A22">
+            <control shapeId="1082" r:id="rId691" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6102,7 +7308,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId450" name="A23">
+            <control shapeId="1083" r:id="rId692" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6124,7 +7330,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId451" name="A24">
+            <control shapeId="1084" r:id="rId693" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6146,7 +7352,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId452" name="A25">
+            <control shapeId="1085" r:id="rId694" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6168,7 +7374,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId453" name="A26">
+            <control shapeId="1086" r:id="rId695" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6190,7 +7396,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId454" name="A27">
+            <control shapeId="1087" r:id="rId696" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6212,7 +7418,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId455" name="A28">
+            <control shapeId="1088" r:id="rId697" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6234,7 +7440,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId456" name="A29">
+            <control shapeId="1089" r:id="rId698" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6256,7 +7462,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId457" name="A30">
+            <control shapeId="1090" r:id="rId699" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6278,7 +7484,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId458" name="A31">
+            <control shapeId="1091" r:id="rId700" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6300,7 +7506,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId459" name="A32">
+            <control shapeId="1092" r:id="rId701" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6322,7 +7528,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId460" name="A33">
+            <control shapeId="1093" r:id="rId702" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6342,6 +7548,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId703" name="A34">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>33</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId704" name="A35">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>34</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>35</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/GF_X-master/AAAGameData/Languages/ChineseTraditional.xlsx
+++ b/GF_X-master/AAAGameData/Languages/ChineseTraditional.xlsx
@@ -3214,6 +3214,286 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3230,7 +3510,93 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1061">
+            <xdr:cNvPr hidden="1" name="A1" id="1060">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1060"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3305,18 +3671,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1062">
+            <xdr:cNvPr hidden="1" name="A3" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -3391,18 +3757,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1063">
+            <xdr:cNvPr hidden="1" name="A4" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -3477,18 +3843,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1064">
+            <xdr:cNvPr hidden="1" name="A5" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -3563,18 +3929,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1065">
+            <xdr:cNvPr hidden="1" name="A6" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -3649,18 +4015,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1066">
+            <xdr:cNvPr hidden="1" name="A7" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -3735,18 +4101,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1067">
+            <xdr:cNvPr hidden="1" name="A8" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -3821,18 +4187,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1068">
+            <xdr:cNvPr hidden="1" name="A9" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -3907,18 +4273,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1069">
+            <xdr:cNvPr hidden="1" name="A10" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -3993,18 +4359,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1070">
+            <xdr:cNvPr hidden="1" name="A11" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1070"/>
@@ -4079,18 +4445,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1071">
+            <xdr:cNvPr hidden="1" name="A12" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -4165,18 +4531,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1072">
+            <xdr:cNvPr hidden="1" name="A13" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -4251,18 +4617,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1073">
+            <xdr:cNvPr hidden="1" name="A14" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -4337,18 +4703,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1074">
+            <xdr:cNvPr hidden="1" name="A15" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -4423,18 +4789,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1075">
+            <xdr:cNvPr hidden="1" name="A16" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -4509,18 +4875,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1076">
+            <xdr:cNvPr hidden="1" name="A17" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -4595,18 +4961,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1077">
+            <xdr:cNvPr hidden="1" name="A18" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -4681,18 +5047,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1078">
+            <xdr:cNvPr hidden="1" name="A19" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -4767,18 +5133,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1079">
+            <xdr:cNvPr hidden="1" name="A20" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -4853,18 +5219,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1080">
+            <xdr:cNvPr hidden="1" name="A21" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -4939,18 +5305,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1081">
+            <xdr:cNvPr hidden="1" name="A22" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -5025,18 +5391,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1082">
+            <xdr:cNvPr hidden="1" name="A23" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -5111,18 +5477,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1083">
+            <xdr:cNvPr hidden="1" name="A24" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -5197,18 +5563,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1084">
+            <xdr:cNvPr hidden="1" name="A25" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -5283,18 +5649,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1085">
+            <xdr:cNvPr hidden="1" name="A26" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -5369,18 +5735,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1086">
+            <xdr:cNvPr hidden="1" name="A27" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -5455,18 +5821,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1087">
+            <xdr:cNvPr hidden="1" name="A28" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -5541,18 +5907,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1088">
+            <xdr:cNvPr hidden="1" name="A29" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -5627,18 +5993,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1089">
+            <xdr:cNvPr hidden="1" name="A30" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -5713,18 +6079,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1090">
+            <xdr:cNvPr hidden="1" name="A31" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -5799,18 +6165,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1091">
+            <xdr:cNvPr hidden="1" name="A32" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -5885,18 +6251,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1092">
+            <xdr:cNvPr hidden="1" name="A33" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -5971,18 +6337,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1093">
+            <xdr:cNvPr hidden="1" name="A34" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -6057,92 +6423,6 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -6154,10 +6434,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1095">
+            <xdr:cNvPr hidden="1" name="A35" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6824,7 +7104,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId670" name="A1">
+            <control shapeId="1060" r:id="rId738" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6846,7 +7126,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId671" name="A2">
+            <control shapeId="1061" r:id="rId739" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6868,7 +7148,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId672" name="A3">
+            <control shapeId="1062" r:id="rId740" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6890,7 +7170,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId673" name="A4">
+            <control shapeId="1063" r:id="rId741" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6912,7 +7192,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId674" name="A5">
+            <control shapeId="1064" r:id="rId742" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6934,7 +7214,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId675" name="A6">
+            <control shapeId="1065" r:id="rId743" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6956,7 +7236,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId676" name="A7">
+            <control shapeId="1066" r:id="rId744" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6978,7 +7258,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId677" name="A8">
+            <control shapeId="1067" r:id="rId745" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7000,7 +7280,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId678" name="A9">
+            <control shapeId="1068" r:id="rId746" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7022,7 +7302,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId679" name="A10">
+            <control shapeId="1069" r:id="rId747" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7044,7 +7324,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId680" name="A11">
+            <control shapeId="1070" r:id="rId748" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7066,7 +7346,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId681" name="A12">
+            <control shapeId="1071" r:id="rId749" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7088,7 +7368,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId682" name="A13">
+            <control shapeId="1072" r:id="rId750" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7110,7 +7390,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId683" name="A14">
+            <control shapeId="1073" r:id="rId751" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7132,7 +7412,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId684" name="A15">
+            <control shapeId="1074" r:id="rId752" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7154,7 +7434,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId685" name="A16">
+            <control shapeId="1075" r:id="rId753" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7176,7 +7456,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId686" name="A17">
+            <control shapeId="1076" r:id="rId754" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7198,7 +7478,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId687" name="A18">
+            <control shapeId="1077" r:id="rId755" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7220,7 +7500,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId688" name="A19">
+            <control shapeId="1078" r:id="rId756" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7242,7 +7522,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId689" name="A20">
+            <control shapeId="1079" r:id="rId757" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7264,7 +7544,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId690" name="A21">
+            <control shapeId="1080" r:id="rId758" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7286,7 +7566,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId691" name="A22">
+            <control shapeId="1081" r:id="rId759" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7308,7 +7588,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId692" name="A23">
+            <control shapeId="1082" r:id="rId760" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7330,7 +7610,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId693" name="A24">
+            <control shapeId="1083" r:id="rId761" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7352,7 +7632,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId694" name="A25">
+            <control shapeId="1084" r:id="rId762" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7374,7 +7654,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId695" name="A26">
+            <control shapeId="1085" r:id="rId763" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7396,7 +7676,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId696" name="A27">
+            <control shapeId="1086" r:id="rId764" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7418,7 +7698,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId697" name="A28">
+            <control shapeId="1087" r:id="rId765" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7440,7 +7720,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId698" name="A29">
+            <control shapeId="1088" r:id="rId766" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7462,7 +7742,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId699" name="A30">
+            <control shapeId="1089" r:id="rId767" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7484,7 +7764,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId700" name="A31">
+            <control shapeId="1090" r:id="rId768" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7506,7 +7786,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId701" name="A32">
+            <control shapeId="1091" r:id="rId769" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7528,7 +7808,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId702" name="A33">
+            <control shapeId="1092" r:id="rId770" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7550,7 +7830,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId703" name="A34">
+            <control shapeId="1093" r:id="rId771" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -7572,7 +7852,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId704" name="A35">
+            <control shapeId="1094" r:id="rId772" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
